--- a/Wordle_Duel_Product_Backlog.xlsx
+++ b/Wordle_Duel_Product_Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/81ab7734a6a69e1a/Documents/Cna/Fall 2025/CP3490 Software Engineering/Wordle_Duel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0851C2B4-1840-4623-96D0-A3D921CC4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{0851C2B4-1840-4623-96D0-A3D921CC4092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E44E62E0-149D-47A7-A6A8-5BBE6C95657E}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="31590" windowHeight="18225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wordle Duel Backlog" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>ID</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Unit tests pass for all valid/invalid word conditions.</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
   </si>
 </sst>
 </file>
@@ -472,7 +478,7 @@
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -512,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,7 +638,7 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -652,7 +658,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
